--- a/artfynd/A 52017-2025 artfynd.xlsx
+++ b/artfynd/A 52017-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539585</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129539324</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129539567</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129540202</v>
       </c>
       <c r="B5" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52017-2025 artfynd.xlsx
+++ b/artfynd/A 52017-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539585</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129539324</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129539567</v>
       </c>
       <c r="B4" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129540202</v>
       </c>
       <c r="B5" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52017-2025 artfynd.xlsx
+++ b/artfynd/A 52017-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539585</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129539324</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129539567</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129540202</v>
       </c>
       <c r="B5" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52017-2025 artfynd.xlsx
+++ b/artfynd/A 52017-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129539324</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129540202</v>
       </c>
       <c r="B5" t="n">
-        <v>78834</v>
+        <v>78839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 52017-2025 artfynd.xlsx
+++ b/artfynd/A 52017-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129539585</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129539324</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129539567</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129540202</v>
       </c>
       <c r="B5" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
